--- a/data/satisfaction_detail/2026/1-6月/住宿团队.xlsx
+++ b/data/satisfaction_detail/2026/1-6月/住宿团队.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>9.94</v>
+        <v>9.93</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="3">
@@ -485,10 +485,10 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>9.85</v>
+        <v>9.83</v>
       </c>
       <c r="C3" s="3" t="n">
-        <v>10</v>
+        <v>9.970000000000001</v>
       </c>
     </row>
     <row r="4">
@@ -498,10 +498,10 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>9.880000000000001</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>10</v>
+        <v>9.98</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>9.76</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="C5" s="4" t="n">
         <v>10</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>9.98</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="C6" s="4" t="n">
         <v>10</v>
@@ -537,10 +537,10 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>9.25</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10</v>
+        <v>9.779999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -550,7 +550,7 @@
         </is>
       </c>
       <c r="B8" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="C8" s="4" t="n">
         <v>10</v>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="B9" s="4" t="n">
-        <v>9.960000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="C9" s="4" t="n">
         <v>10</v>
